--- a/docs/dossiers/dossier-paris-10e-73bf3abe.xlsx
+++ b/docs/dossiers/dossier-paris-10e-73bf3abe.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-73bf3abe.xlsx
+++ b/docs/dossiers/dossier-paris-10e-73bf3abe.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-73bf3abe.xlsx
+++ b/docs/dossiers/dossier-paris-10e-73bf3abe.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-73bf3abe.xlsx
+++ b/docs/dossiers/dossier-paris-10e-73bf3abe.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-73bf3abe.xlsx
+++ b/docs/dossiers/dossier-paris-10e-73bf3abe.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-73bf3abe.xlsx
+++ b/docs/dossiers/dossier-paris-10e-73bf3abe.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-73bf3abe.xlsx
+++ b/docs/dossiers/dossier-paris-10e-73bf3abe.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-73bf3abe.xlsx
+++ b/docs/dossiers/dossier-paris-10e-73bf3abe.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-73bf3abe.xlsx
+++ b/docs/dossiers/dossier-paris-10e-73bf3abe.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-10e-73bf3abe.xlsx
+++ b/docs/dossiers/dossier-paris-10e-73bf3abe.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +473 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +456 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0475</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-10e-73bf3abe.xlsx
+++ b/docs/dossiers/dossier-paris-10e-73bf3abe.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
